--- a/demo-imports/listino-alfa-medical-2028.xlsx
+++ b/demo-imports/listino-alfa-medical-2028.xlsx
@@ -425,7 +425,7 @@
     <t>NovaKit</t>
   </si>
   <si>
-    <t>8099999999999</t>
+    <t>8099999999992</t>
   </si>
   <si>
     <t>DPI</t>
